--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6825,8 +6825,8 @@
       <c r="P60" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" s="9" t="n">
-        <v>0</v>
+      <c r="Q60" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R60" s="9" t="n">
         <v>0</v>
@@ -15306,7 +15306,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,11 @@
       <c r="AB16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2866,7 +2870,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -4417,7 +4425,11 @@
       <c r="AB36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -6861,7 +6873,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7572,7 +7588,11 @@
       <c r="AB67" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC67" s="4" t="inlineStr"/>
+      <c r="AC67" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -8598,7 +8618,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -8901,7 +8925,11 @@
       <c r="AB80" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC80" s="4" t="inlineStr"/>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9810,7 +9838,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -9911,7 +9943,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10012,7 +10048,11 @@
       <c r="AB91" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10517,7 +10557,11 @@
       <c r="AB96" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC96" s="4" t="inlineStr"/>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -11531,7 +11575,11 @@
       <c r="AB106" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -12036,7 +12084,11 @@
       <c r="AB111" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -14787,7 +14839,11 @@
       <c r="AB138" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC138" s="4" t="inlineStr"/>
+      <c r="AC138" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC138"/>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 56 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 51 clubs short</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="9" t="n">
         <v>0</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3996,8 +3996,8 @@
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
@@ -6497,13 +6497,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6732,8 +6732,8 @@
       <c r="P59" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" s="9" t="n">
-        <v>1</v>
+      <c r="Q59" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>0</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7478,8 +7478,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7789,8 +7789,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9021,8 +9021,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="10" t="n">
-        <v>1</v>
+      <c r="Z81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -11193,7 +11193,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11263,8 +11263,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -12518,7 +12518,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12588,8 +12588,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -13742,7 +13742,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13812,8 +13812,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -14093,7 +14093,7 @@
         <v>0</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -15164,7 +15164,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15329,7 +15329,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15428,7 +15428,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15494,7 +15494,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15659,7 +15659,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15758,7 +15758,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -15824,7 +15824,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 51 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1097,8 +1097,8 @@
       <c r="P4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="9" t="n">
-        <v>1</v>
+      <c r="Q4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1936,8 +1936,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2453,8 +2453,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2527,8 +2527,8 @@
       <c r="P18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="9" t="n">
-        <v>0</v>
+      <c r="Q18" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2966,8 +2966,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4693,8 +4693,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P39" s="9" t="n">
-        <v>2</v>
+      <c r="P39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>1</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5539,8 +5539,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5943,8 +5943,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="9" t="n">
         <v>0</v>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6246,8 +6246,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -7664,7 +7664,7 @@
         <v>0</v>
       </c>
       <c r="S68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -8337,7 +8337,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8407,8 +8407,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9000,8 +9000,8 @@
       <c r="R81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S81" s="9" t="n">
-        <v>0</v>
+      <c r="S81" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T81" s="9" t="n">
         <v>0</v>
@@ -9021,8 +9021,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9627,8 +9627,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9934,8 +9934,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10144,8 +10144,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="9" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10447,8 +10447,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -11294,7 +11294,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11364,8 +11364,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11447,8 +11447,8 @@
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
@@ -11465,8 +11465,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12180,8 +12180,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12790,8 +12790,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12976,7 +12976,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" s="9" t="n">
         <v>0</v>
@@ -13439,7 +13439,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13509,8 +13509,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -13786,7 +13786,7 @@
         <v>0</v>
       </c>
       <c r="Q128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14422,8 +14422,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -14933,7 +14933,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14999,7 +14999,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15032,7 +15032,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15065,7 +15065,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15197,7 +15197,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15263,7 +15263,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15296,7 +15296,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15461,7 +15461,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15494,7 +15494,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15560,7 +15560,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15626,7 +15626,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15659,7 +15659,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15692,7 +15692,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -15758,7 +15758,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -15824,7 +15824,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -15890,7 +15890,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1068,17 +1068,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>2</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2082,17 +2082,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="10" t="n">
         <v>2</v>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2805,13 +2805,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2849,11 +2849,11 @@
       <c r="U21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="9" t="n">
-        <v>0</v>
+      <c r="V21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W21" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3011,17 +3011,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3524,17 +3524,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -3572,7 +3572,7 @@
         <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>4</v>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>1</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="9" t="n">
         <v>0</v>
@@ -3839,13 +3839,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3940,13 +3940,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4255,17 +4255,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4360,17 +4360,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>0</v>
@@ -4566,13 +4566,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4667,17 +4667,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4974,17 +4974,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -5019,7 +5019,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5382,13 +5382,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
@@ -5584,13 +5584,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5685,13 +5685,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5786,13 +5786,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5988,13 +5988,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6089,13 +6089,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6291,13 +6291,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6392,13 +6392,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6497,13 +6497,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6703,13 +6703,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6808,13 +6808,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -6913,17 +6913,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6961,7 +6961,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>5</v>
@@ -7014,13 +7014,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7115,13 +7115,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7216,17 +7216,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7321,13 +7321,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7422,13 +7422,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7463,11 +7463,11 @@
       <c r="T66" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U66" s="9" t="n">
-        <v>0</v>
+      <c r="U66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7628,17 +7628,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7733,13 +7733,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7838,17 +7838,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7943,13 +7943,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8044,13 +8044,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8149,13 +8149,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8351,13 +8351,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -8396,7 +8396,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8553,13 +8553,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8658,13 +8658,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8759,13 +8759,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8860,13 +8860,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>7</v>
+        <v>-9</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9009,11 +9009,11 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
-        <v>3</v>
+      <c r="V81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>7</v>
@@ -9066,13 +9066,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9167,13 +9167,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9268,13 +9268,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9369,17 +9369,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -9417,7 +9417,7 @@
         <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>4</v>
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9571,13 +9571,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9672,13 +9672,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9773,13 +9773,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9817,8 +9817,8 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>3</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9878,17 +9878,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9983,13 +9983,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10088,13 +10088,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -10189,17 +10189,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10290,13 +10290,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10492,13 +10492,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>4</v>
       </c>
       <c r="W96" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>7</v>
@@ -10597,13 +10597,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10698,13 +10698,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>1</v>
@@ -10743,7 +10743,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10799,13 +10799,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10900,17 +10900,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10945,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11005,13 +11005,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101" s="9" t="n">
         <v>0</v>
@@ -11106,17 +11106,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11409,13 +11409,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11510,13 +11510,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11716,17 +11716,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11817,13 +11817,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11918,13 +11918,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12019,13 +12019,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12063,11 +12063,11 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>3</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>7</v>
@@ -12124,13 +12124,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12225,13 +12225,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12431,13 +12431,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12532,17 +12532,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12576,11 +12576,11 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W116" s="9" t="n">
-        <v>0</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W116" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>7</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12677,11 +12677,11 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="9" t="n">
-        <v>3</v>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X117" s="9" t="n">
         <v>1</v>
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12734,17 +12734,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12775,8 +12775,8 @@
       <c r="T118" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U118" s="9" t="n">
-        <v>0</v>
+      <c r="U118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V118" s="9" t="n">
         <v>0</v>
@@ -12839,13 +12839,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12940,13 +12940,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12975,8 +12975,8 @@
       <c r="R120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S120" s="9" t="n">
-        <v>1</v>
+      <c r="S120" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T120" s="9" t="n">
         <v>0</v>
@@ -13041,13 +13041,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>4</v>
       </c>
       <c r="W121" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>5</v>
@@ -13132,7 +13132,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13146,13 +13146,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13184,14 +13184,14 @@
       <c r="S122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13352,13 +13352,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13453,13 +13453,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13554,13 +13554,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13756,17 +13756,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13861,17 +13861,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13962,13 +13962,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -14063,13 +14063,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14265,13 +14265,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14309,11 +14309,11 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>3</v>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X133" s="9" t="n">
         <v>2</v>
@@ -14467,13 +14467,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14568,13 +14568,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14669,13 +14669,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14774,13 +14774,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -15014,7 +15014,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -15065,13 +15065,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -15080,7 +15080,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -15146,7 +15146,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -15179,7 +15179,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15212,7 +15212,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15245,7 +15245,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15377,7 +15377,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -15395,7 +15395,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15410,7 +15410,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -15443,7 +15443,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15494,7 +15494,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15542,7 +15542,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -15560,7 +15560,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15575,7 +15575,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -15608,7 +15608,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -15674,7 +15674,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -15707,7 +15707,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -15725,7 +15725,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -15758,7 +15758,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -15791,7 +15791,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -15839,7 +15839,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -15857,7 +15857,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1315,8 +1315,8 @@
       <c r="T6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U6" s="9" t="n">
-        <v>0</v>
+      <c r="U6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2330,8 +2330,8 @@
       <c r="S16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T16" s="9" t="n">
-        <v>0</v>
+      <c r="T16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="9" t="n">
         <v>0</v>
@@ -2846,8 +2846,8 @@
       <c r="T21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U21" s="9" t="n">
-        <v>0</v>
+      <c r="U21" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V21" s="10" t="n">
         <v>4</v>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3524,13 +3524,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>4</v>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3839,13 +3839,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -4075,7 +4075,7 @@
         <v>1</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>0</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="9" t="n">
         <v>0</v>
@@ -4360,13 +4360,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4917,8 +4917,8 @@
       <c r="U41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="9" t="n">
-        <v>3</v>
+      <c r="V41" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="9" t="n">
         <v>0</v>
@@ -5115,7 +5115,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="9" t="n">
         <v>0</v>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U47" s="9" t="n">
         <v>0</v>
@@ -5584,13 +5584,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5685,13 +5685,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7451,8 +7451,8 @@
       <c r="P66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" s="9" t="n">
-        <v>1</v>
+      <c r="Q66" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7943,13 +7943,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" s="10" t="n">
         <v>1</v>
@@ -8860,13 +8860,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>1</v>
       </c>
       <c r="Q84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
@@ -9773,13 +9773,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -10088,13 +10088,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10189,17 +10189,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-21</v>
-      </c>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10635,8 +10635,8 @@
       <c r="S97" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
@@ -10835,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="S99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" s="9" t="n">
         <v>0</v>
@@ -13352,13 +13352,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -14568,13 +14568,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -14933,13 +14933,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -15032,7 +15032,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15065,7 +15065,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -15230,7 +15230,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15263,7 +15263,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15608,7 +15608,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -15626,7 +15626,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/101/inyear.xlsx
+++ b/docs/d/101/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="9" t="n">
         <v>0</v>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4360,13 +4360,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4398,8 +4398,8 @@
       <c r="S36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="9" t="n">
-        <v>0</v>
+      <c r="T36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U36" s="9" t="n">
         <v>0</v>
@@ -4566,13 +4566,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>4</v>
       </c>
       <c r="W41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>4</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5821,8 +5821,8 @@
       <c r="R50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="9" t="n">
-        <v>1</v>
+      <c r="S50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T50" s="10" t="n">
         <v>1</v>
@@ -6598,13 +6598,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>5</v>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -9268,13 +9268,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>1</v>
       </c>
       <c r="U84" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V84" s="9" t="n">
         <v>2</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>1</v>
@@ -10326,7 +10326,7 @@
         <v>0</v>
       </c>
       <c r="S94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" s="9" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q96" s="10" t="n">
         <v>2</v>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10900,17 +10900,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L100" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10944,8 +10944,8 @@
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>3</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11716,13 +11716,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>1</v>
@@ -14063,13 +14063,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14265,13 +14265,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14704,8 +14704,8 @@
       <c r="R137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S137" s="9" t="n">
-        <v>1</v>
+      <c r="S137" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T137" s="9" t="n">
         <v>0</v>
@@ -15197,7 +15197,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15263,7 +15263,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15659,7 +15659,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15674,7 +15674,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -15890,7 +15890,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
